--- a/data/trans_dic/IP12B$fiebre-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,23</t>
+          <t>0,0; 43,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,09</t>
+          <t>0,0; 74,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,16</t>
+          <t>0,0; 39,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,26</t>
+          <t>0,0; 51,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,08</t>
+          <t>0,0; 55,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,42</t>
+          <t>0,0; 38,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 33,63</t>
+          <t>4,42; 34,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 54,54</t>
+          <t>7,51; 57,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 31,79</t>
+          <t>4,37; 33,36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,94</t>
+          <t>0,0; 31,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,79</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 33,44</t>
+          <t>4,37; 33,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,27</t>
+          <t>0,0; 41,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,79</t>
+          <t>0,0; 27,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 24,64</t>
+          <t>2,44; 22,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,42</t>
+          <t>0,0; 19,47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,74</t>
+          <t>0,0; 36,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,33</t>
+          <t>0,0; 79,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,05</t>
+          <t>0,0; 36,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,07</t>
+          <t>0,0; 42,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,69</t>
+          <t>0,0; 26,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,1</t>
+          <t>0,0; 48,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,29</t>
+          <t>0,0; 52,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,36</t>
+          <t>0,0; 34,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,08</t>
+          <t>0,0; 36,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,48</t>
+          <t>0,0; 16,58</t>
         </is>
       </c>
     </row>
@@ -1122,22 +1123,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,76</t>
+          <t>0,0; 51,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,0</t>
+          <t>0,0; 69,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,81</t>
+          <t>0,0; 68,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1152,19 +1153,19 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 42,94</t>
+          <t>5,2; 41,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 65,91</t>
+          <t>8,47; 67,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,47</t>
+          <t>0,0; 79,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,21</t>
+          <t>0,0; 61,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,84</t>
+          <t>0,0; 81,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,1</t>
+          <t>0,0; 51,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,61</t>
+          <t>0,0; 33,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,52</t>
+          <t>0,0; 36,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1347,37 +1348,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,37</t>
+          <t>0,0; 56,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,55</t>
+          <t>0,0; 63,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 83,69</t>
+          <t>12,16; 83,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,93</t>
+          <t>0,0; 30,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,88</t>
+          <t>0,0; 36,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,54; 55,73</t>
+          <t>11,27; 52,16</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,54</t>
+          <t>0,0; 52,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,78; 50,16</t>
+          <t>11,08; 50,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,66</t>
+          <t>0,0; 23,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 49,01</t>
+          <t>6,36; 51,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 45,45</t>
+          <t>5,78; 44,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>0,0; 22,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 42,67</t>
+          <t>7,44; 39,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,93; 40,14</t>
+          <t>12,33; 39,33</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,36</t>
+          <t>1,51; 13,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,85</t>
+          <t>6,89; 21,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,74; 22,62</t>
+          <t>7,51; 23,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,06</t>
+          <t>5,35; 19,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,62; 27,04</t>
+          <t>8,93; 25,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,29; 26,81</t>
+          <t>9,32; 26,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,62</t>
+          <t>4,37; 14,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,37; 20,15</t>
+          <t>9,51; 20,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,8</t>
+          <t>9,25; 20,59</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2515</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3694</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3601</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4087</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4549</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3852</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>602; 4693</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>989; 7517</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>843; 6439</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2562</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3846</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3886</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>608; 4645</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3354</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4375</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>635; 5835</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3352</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2960</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2488</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2675</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2635</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4126</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3310</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3337</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5400</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3237</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2967</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1333</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4284</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4357</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1784</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1998</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>767; 6083</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>533; 4231</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2907</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3192</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2498</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3500</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3471</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2744</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2865</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3343</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3823</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>589; 4056</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3491</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4819</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1217; 5632</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>5699</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3620</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1502; 6796</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3213</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>658; 5309</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>594; 4612</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4388</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1281; 6883</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2939; 9378</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>18034</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>663; 5848</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4221; 13253</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4141; 12848</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2498; 9219</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>5674; 16080</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4462; 12443</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3959; 12714</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>11872; 25853</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>9521; 21208</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$fiebre-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,91</t>
+          <t>0,0; 44,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,71</t>
+          <t>0,0; 77,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,28</t>
+          <t>0,0; 39,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,79</t>
+          <t>0,0; 46,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,29</t>
+          <t>0,0; 63,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,01</t>
+          <t>0,0; 46,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 34,45</t>
+          <t>4,36; 37,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 57,07</t>
+          <t>7,43; 51,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 33,36</t>
+          <t>4,04; 34,91</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 23,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,77</t>
+          <t>0,0; 57,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 33,4</t>
+          <t>4,34; 33,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,88</t>
+          <t>0,0; 48,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,12</t>
+          <t>0,0; 25,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 22,4</t>
+          <t>2,42; 22,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,47</t>
+          <t>0,0; 25,83</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,89</t>
+          <t>0,0; 37,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,74</t>
+          <t>0,0; 38,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,78</t>
+          <t>0,0; 42,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,97</t>
+          <t>0,0; 26,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,15</t>
+          <t>0,0; 46,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,11</t>
+          <t>0,0; 55,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,47</t>
+          <t>0,0; 28,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,27</t>
+          <t>0,0; 34,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,58</t>
+          <t>0,0; 16,41</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,06</t>
+          <t>0,0; 46,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,27</t>
+          <t>0,0; 71,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,42</t>
+          <t>0,0; 60,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 41,21</t>
+          <t>4,99; 44,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 67,21</t>
+          <t>8,36; 60,35</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,13</t>
+          <t>0,0; 61,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,06</t>
+          <t>0,0; 78,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,9</t>
+          <t>0,0; 52,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,84</t>
+          <t>0,0; 32,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,24</t>
+          <t>0,0; 53,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,03</t>
+          <t>0,0; 39,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,17</t>
+          <t>0,0; 62,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,3</t>
+          <t>0,0; 56,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,16; 83,68</t>
+          <t>12,15; 83,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,06</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,52</t>
+          <t>0,0; 39,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,27; 52,16</t>
+          <t>11,17; 54,77</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,61</t>
+          <t>0,0; 53,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,08; 50,11</t>
+          <t>10,56; 50,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,12</t>
+          <t>0,0; 25,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 51,29</t>
+          <t>6,31; 51,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 44,87</t>
+          <t>5,91; 44,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,28</t>
+          <t>0,0; 16,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 39,94</t>
+          <t>7,21; 39,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,33; 39,33</t>
+          <t>12,75; 40,19</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,33</t>
+          <t>1,51; 14,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 21,62</t>
+          <t>6,78; 20,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 23,31</t>
+          <t>7,36; 22,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,35; 19,74</t>
+          <t>5,49; 20,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,93; 25,3</t>
+          <t>8,06; 24,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 26,0</t>
+          <t>9,11; 26,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,04</t>
+          <t>4,96; 14,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,71</t>
+          <t>9,88; 20,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,25; 20,59</t>
+          <t>10,26; 20,5</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2515</t>
+          <t>0; 2531</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3694</t>
+          <t>0; 3835</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3601</t>
+          <t>0; 3578</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4087</t>
+          <t>0; 3670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 5195</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>0; 4689</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>602; 4693</t>
+          <t>593; 5173</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>989; 7517</t>
+          <t>979; 6836</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>843; 6439</t>
+          <t>779; 6738</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3846</t>
+          <t>0; 2840</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 3353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>608; 4645</t>
+          <t>603; 4687</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 3866</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4057</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>635; 5835</t>
+          <t>631; 5854</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 4449</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>0; 3005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2675</t>
+          <t>0; 2792</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2635</t>
+          <t>0; 2639</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 4030</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 3991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3310</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3337</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5400</t>
+          <t>0; 5081</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3237</t>
+          <t>0; 3205</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4284</t>
+          <t>0; 3872</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>0; 3838</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>767; 6083</t>
+          <t>737; 6602</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>533; 4231</t>
+          <t>526; 3799</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3192</t>
+          <t>0; 3214</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2498</t>
+          <t>0; 2430</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3500</t>
+          <t>0; 3559</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3471</t>
+          <t>0; 3291</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2744</t>
+          <t>0; 4069</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2865</t>
+          <t>0; 2821</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3343</t>
+          <t>0; 3729</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 3429</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3491</t>
+          <t>0; 3352</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4819</t>
+          <t>0; 5214</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1217; 5632</t>
+          <t>1206; 5914</t>
         </is>
       </c>
     </row>
@@ -3007,42 +3007,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3620</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1502; 6796</t>
+          <t>1432; 6913</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3213</t>
+          <t>0; 3504</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>658; 5309</t>
+          <t>653; 5345</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>594; 4612</t>
+          <t>608; 4541</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>0; 3272</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1281; 6883</t>
+          <t>1242; 6809</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2939; 9378</t>
+          <t>3041; 9582</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>663; 5848</t>
+          <t>661; 6276</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4221; 13253</t>
+          <t>4156; 12806</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4141; 12848</t>
+          <t>4059; 12160</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2498; 9219</t>
+          <t>2566; 9752</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5674; 16080</t>
+          <t>5124; 15427</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4462; 12443</t>
+          <t>4358; 12783</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3959; 12714</t>
+          <t>4495; 12777</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11872; 25853</t>
+          <t>12336; 26100</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9521; 21208</t>
+          <t>10561; 21110</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$fiebre-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,01%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>32,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,54%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,01%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,19</t>
+          <t>0,0; 51,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,55</t>
+          <t>0,0; 60,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,03</t>
+          <t>0,0; 38,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,51</t>
+          <t>0,0; 45,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,14</t>
+          <t>0,0; 71,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,26</t>
+          <t>0,0; 47,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 37,98</t>
+          <t>4,31; 33,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 51,9</t>
+          <t>7,41; 54,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 34,91</t>
+          <t>4,21; 31,79</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,4</t>
+          <t>4,32; 33,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 33,7</t>
+          <t>0,0; 24,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,15</t>
+          <t>0,0; 24,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 22,48</t>
+          <t>2,47; 24,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,83</t>
+          <t>0,0; 22,42</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,45%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 79,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,46</t>
+          <t>0,0; 38,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,35</t>
+          <t>0,0; 35,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,83</t>
+          <t>0,0; 42,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,33</t>
+          <t>0,0; 27,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,74</t>
+          <t>0,0; 65,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,5</t>
+          <t>0,0; 44,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,13</t>
+          <t>0,0; 36,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 18,48</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30,97%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>46,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17,11%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>27,16%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 59,81</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 46,15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 71,38</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,27</t>
+          <t>0,0; 50,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 71,0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 44,73</t>
+          <t>4,85; 42,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 60,35</t>
+          <t>8,41; 65,91</t>
         </is>
       </c>
     </row>
@@ -1175,27 +1175,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>18,3%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>16,28%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,38</t>
+          <t>0,0; 78,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,84</t>
+          <t>0,0; 73,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 61,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,77</t>
+          <t>0,0; 58,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,08</t>
+          <t>0,0; 32,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20,84%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,42</t>
+          <t>0,0; 60,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,66</t>
+          <t>12,39; 83,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,77</t>
+          <t>0,0; 40,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,15; 83,68</t>
+          <t>0,0; 58,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,86</t>
+          <t>0,0; 23,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,51</t>
+          <t>0,0; 35,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,17; 54,77</t>
+          <t>11,54; 55,73</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>17,64%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>27,81%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,21</t>
+          <t>6,32; 49,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,56; 50,98</t>
+          <t>5,89; 45,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,31; 51,63</t>
+          <t>0,0; 53,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 44,18</t>
+          <t>12,78; 50,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,61</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 39,51</t>
+          <t>7,27; 42,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,75; 40,19</t>
+          <t>11,93; 40,14</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>13,73%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,3</t>
+          <t>5,35; 20,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,78; 20,89</t>
+          <t>9,62; 27,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 22,06</t>
+          <t>9,29; 26,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,88</t>
+          <t>1,44; 13,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,27</t>
+          <t>7,14; 21,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,11; 26,71</t>
+          <t>7,74; 22,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,11</t>
+          <t>4,38; 13,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,88; 20,91</t>
+          <t>9,37; 20,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,26; 20,5</t>
+          <t>9,97; 20,8</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1631</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1333</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1811</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2531</t>
+          <t>0; 4046</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3835</t>
+          <t>0; 4943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3578</t>
+          <t>0; 3894</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3670</t>
+          <t>0; 2590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5195</t>
+          <t>0; 3516</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4689</t>
+          <t>0; 4323</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>593; 5173</t>
+          <t>587; 4581</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>979; 6836</t>
+          <t>977; 7184</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>779; 6738</t>
+          <t>813; 6137</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2840</t>
+          <t>601; 4650</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>603; 4687</t>
+          <t>0; 3027</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4057</t>
+          <t>0; 3999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>631; 5854</t>
+          <t>644; 6418</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4449</t>
+          <t>0; 3861</t>
         </is>
       </c>
     </row>
@@ -2081,22 +2081,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2134,27 +2134,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>678</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2489</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3005</t>
+          <t>0; 2770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2488</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2792</t>
+          <t>0; 2867</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2639</t>
+          <t>0; 2592</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4030</t>
+          <t>0; 4236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2254,22 +2254,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2302,27 +2302,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 4147</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3526</t>
+          <t>0; 3765</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2772</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5081</t>
+          <t>0; 5372</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3205</t>
+          <t>0; 3609</t>
         </is>
       </c>
     </row>
@@ -2417,22 +2417,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1225</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,32 +2513,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3809</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1784</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0; 1333</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3872</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3220</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3838</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1784</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>737; 6602</t>
+          <t>716; 6337</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>526; 3799</t>
+          <t>530; 4149</t>
         </is>
       </c>
     </row>
@@ -2575,22 +2575,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>670</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>850</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2907</t>
+          <t>0; 2430</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3214</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2430</t>
+          <t>0; 2691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3196</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3559</t>
+          <t>0; 3918</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3291</t>
+          <t>0; 3344</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1240</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2821</t>
+          <t>0; 3657</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3729</t>
+          <t>601; 4056</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2841</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3429</t>
+          <t>0; 2866</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>589; 4056</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 2780</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5214</t>
+          <t>0; 4734</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1206; 5914</t>
+          <t>1246; 6018</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1214</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3771</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2286</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3661</t>
+          <t>654; 5074</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1432; 6913</t>
+          <t>606; 4672</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3504</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>653; 5345</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>608; 4541</t>
+          <t>1732; 6802</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3272</t>
+          <t>0; 3528</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1242; 6809</t>
+          <t>1252; 7354</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3041; 9582</t>
+          <t>2843; 9569</t>
         </is>
       </c>
     </row>
@@ -3059,27 +3059,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2564</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>8010</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>7570</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>10024</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7756</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>661; 6276</t>
+          <t>2501; 9368</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4156; 12806</t>
+          <t>6114; 17188</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4059; 12160</t>
+          <t>4446; 12831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2566; 9752</t>
+          <t>632; 5862</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5124; 15427</t>
+          <t>4374; 13392</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4358; 12783</t>
+          <t>4268; 12467</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4495; 12777</t>
+          <t>3964; 12340</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>12336; 26100</t>
+          <t>11696; 25154</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10561; 21110</t>
+          <t>10270; 21420</t>
         </is>
       </c>
     </row>
